--- a/yellow-server/data/results/result.xlsx
+++ b/yellow-server/data/results/result.xlsx
@@ -64,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AE11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -501,7 +502,7 @@
       <c r="B2" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="1" t="str">
         <v>310227199002301001</v>
       </c>
       <c r="D2" t="str">
@@ -520,10 +521,10 @@
         <v>高</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>恒大名都小区</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>小区</v>
       </c>
       <c r="K2" t="str">
         <v>同住人</v>
@@ -539,7 +540,7 @@
         <v>嫖娼,卖淫</v>
       </c>
       <c r="O2" t="str">
-        <v>2025年5月22日，根据警企协作获得线索，发现上海市松江区车墩镇张三等人卖淫嫖娼的违法行为，后续进一步开展侦办。</v>
+        <v>2025年5月22日，根据警企协作获得线索，发现上海市松江区车墩镇恒大名都小区张三等人卖淫嫖娼的违法行为，后续进一步开展侦办。</v>
       </c>
       <c r="P2" t="str">
         <v>- 20251001121212 - 商品: &lt;span style='color:red'&gt;名流之夜 玻尿酸夜场套超薄超润滑避孕套 50只/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (123)</v>
@@ -548,15 +549,15 @@
         <v/>
       </c>
       <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v>1</v>
-      </c>
-      <c r="T2" t="str">
-        <v>1</v>
-      </c>
-      <c r="U2" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
         <v>1</v>
       </c>
       <c r="V2">
@@ -597,7 +598,7 @@
       <c r="B3" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="1" t="str">
         <v>310227199002301002</v>
       </c>
       <c r="D3" t="str">
@@ -644,15 +645,15 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v>1</v>
-      </c>
-      <c r="T3" t="str">
-        <v>1</v>
-      </c>
-      <c r="U3" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
@@ -693,7 +694,7 @@
       <c r="B4" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="1" t="str">
         <v>310227199002301003</v>
       </c>
       <c r="D4" t="str">
@@ -740,15 +741,15 @@
         <v/>
       </c>
       <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v>1</v>
-      </c>
-      <c r="T4" t="str">
-        <v>1</v>
-      </c>
-      <c r="U4" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
         <v>1</v>
       </c>
       <c r="V4">
@@ -789,7 +790,7 @@
       <c r="B5" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="1" t="str">
         <v>310227199002301004</v>
       </c>
       <c r="D5" t="str">
@@ -808,10 +809,10 @@
         <v>低</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>松江区西山路81弄某SPA</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>场所</v>
       </c>
       <c r="K5" t="str">
         <v>同住人</v>
@@ -827,7 +828,7 @@
         <v>卖淫</v>
       </c>
       <c r="O5" t="str">
-        <v>根据分局治安支队下发线索，松江区某SPA内有涉黄情况。</v>
+        <v>根据分局治安支队下发线索，松江区西山路81弄某SPA内有涉黄情况。</v>
       </c>
       <c r="P5" t="str">
         <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;【白云山】医用男科洗液30ml/盒男性阴部日常清洁洗护改善包皮炎龟头炎男性家用常备红点瘙痒×1;&lt;/span&gt; - 收货地址：松江公寓 (125)</v>
@@ -836,15 +837,15 @@
         <v>上海企业发展有限公司</v>
       </c>
       <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v>1</v>
-      </c>
-      <c r="T5" t="str">
-        <v>1</v>
-      </c>
-      <c r="U5" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
         <v>1</v>
       </c>
       <c r="V5">
@@ -885,7 +886,7 @@
       <c r="B6" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="1" t="str">
         <v>310227199002301005</v>
       </c>
       <c r="D6" t="str">
@@ -923,7 +924,7 @@
         <v>卖淫</v>
       </c>
       <c r="O6" t="str">
-        <v>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现小王等人有卖淫嫖娼的行为。</v>
+        <v>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现松江区迪萨社区小王等人有卖淫嫖娼的行为。</v>
       </c>
       <c r="P6" t="str">
         <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;【白云山】医用男科洗液30ml/盒男性阴部日常清洁洗护改善包皮炎龟头炎男性家用常备红点瘙痒×1;&lt;/span&gt; - 收货地址：松江公寓 (126)</v>
@@ -932,15 +933,15 @@
         <v>上海电子商务有限公司</v>
       </c>
       <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v>1</v>
-      </c>
-      <c r="T6" t="str">
-        <v>1</v>
-      </c>
-      <c r="U6" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
         <v>1</v>
       </c>
       <c r="V6">
@@ -981,7 +982,7 @@
       <c r="B7" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" s="1" t="str">
         <v>310227199002301006</v>
       </c>
       <c r="D7" t="str">
@@ -1000,10 +1001,10 @@
         <v>低</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>桃园路90号</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>其他</v>
       </c>
       <c r="K7" t="str">
         <v>同住人</v>
@@ -1019,7 +1020,7 @@
         <v>卖淫</v>
       </c>
       <c r="O7" t="str">
-        <v>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现小李等人有卖淫嫖娼的行为。</v>
+        <v>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现松江区桃园路90号小李等人有卖淫嫖娼的行为。</v>
       </c>
       <c r="P7" t="str">
         <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (127)</v>
@@ -1028,15 +1029,15 @@
         <v>上海电子商务有限公司</v>
       </c>
       <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v>1</v>
-      </c>
-      <c r="T7" t="str">
-        <v>1</v>
-      </c>
-      <c r="U7" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
         <v>1</v>
       </c>
       <c r="V7">
@@ -1077,7 +1078,7 @@
       <c r="B8" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="1" t="str">
         <v>310227199002301007</v>
       </c>
       <c r="D8" t="str">
@@ -1096,10 +1097,10 @@
         <v>低</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>桃园路90号</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>其他</v>
       </c>
       <c r="K8" t="str">
         <v>同住人</v>
@@ -1115,7 +1116,7 @@
         <v>嫖娼,卖淫</v>
       </c>
       <c r="O8" t="str">
-        <v>2025年5月14日，我所民警接线索举报称上海市松江区某地有卖淫嫖娼的情况，遂至上址检查，并经出示证件将相关人员传唤至所作进一步调查。</v>
+        <v>2025年5月14日，我所民警接线索举报称上海市松江区桃园路90号有卖淫嫖娼的情况，遂至上址检查，并经出示证件将相关人员传唤至所作进一步调查。</v>
       </c>
       <c r="P8" t="str">
         <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (128)</v>
@@ -1124,15 +1125,15 @@
         <v>上海电子商务有限公司</v>
       </c>
       <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str">
-        <v>1</v>
-      </c>
-      <c r="T8" t="str">
-        <v>1</v>
-      </c>
-      <c r="U8" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
         <v>1</v>
       </c>
       <c r="V8">
@@ -1173,7 +1174,7 @@
       <c r="B9" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" s="1" t="str">
         <v>310227199002301008</v>
       </c>
       <c r="D9" t="str">
@@ -1192,7 +1193,7 @@
         <v>中</v>
       </c>
       <c r="I9" t="str">
-        <v>一二三路111弄-1号商务中心11楼1101室内</v>
+        <v>一二三路111弄-1号商务中心</v>
       </c>
       <c r="J9" t="str">
         <v>商务楼</v>
@@ -1220,15 +1221,15 @@
         <v>上海实业有限公司</v>
       </c>
       <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str">
-        <v>1</v>
-      </c>
-      <c r="T9" t="str">
-        <v>1</v>
-      </c>
-      <c r="U9" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
         <v>1</v>
       </c>
       <c r="V9">
@@ -1269,7 +1270,7 @@
       <c r="B10" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="1" t="str">
         <v>310227199002301009</v>
       </c>
       <c r="D10" t="str">
@@ -1288,7 +1289,7 @@
         <v>中</v>
       </c>
       <c r="I10" t="str">
-        <v>一二三路111弄-1号商务中心11楼1101室内</v>
+        <v>一二三路111弄-1号商务中心</v>
       </c>
       <c r="J10" t="str">
         <v>商务楼</v>
@@ -1316,15 +1317,15 @@
         <v>上海实业有限公司</v>
       </c>
       <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str">
-        <v>1</v>
-      </c>
-      <c r="T10" t="str">
-        <v>1</v>
-      </c>
-      <c r="U10" t="str">
+        <v>尊享SPA(洗脚店)</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
         <v>1</v>
       </c>
       <c r="V10">
@@ -1365,8 +1366,8 @@
       <c r="B11" t="str">
         <v>居民身份证</v>
       </c>
-      <c r="C11" t="str">
-        <v>310227199002301000</v>
+      <c r="C11" s="1" t="str">
+        <v>310227199002301010</v>
       </c>
       <c r="D11" t="str">
         <v>15286493075</v>
@@ -1381,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>中</v>
       </c>
       <c r="I11" t="str">
-        <v>一二三路111弄-1号商务中心11楼1101室内</v>
+        <v>一二三路111弄-1号商务中心</v>
       </c>
       <c r="J11" t="str">
         <v>商务楼</v>
@@ -1406,21 +1407,21 @@
         <v>2025年5月13日，经群众匿名举报，在上海市松江区一二三路111弄-1号商务中心11楼1101室内，有卖淫嫖娼活动。已接报</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>- 20251001121212 - 商品: &lt;span style='color:darkorange'&gt;一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×11;一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×1;三得利 沁桃水饮料 550ml/瓶×5;三得利 沁葡水白葡萄味饮料550ml/瓶果味饮品休闲饮料×5;&lt;/span&gt; - 收货地址：养生SPA (养生spa)</v>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>上海实业有限公司</v>
       </c>
       <c r="R11" t="str">
         <v>尊享SPA(洗脚店)</v>
       </c>
-      <c r="S11" t="str">
-        <v>1</v>
-      </c>
-      <c r="T11" t="str">
-        <v>1</v>
-      </c>
-      <c r="U11" t="str">
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
         <v>1</v>
       </c>
       <c r="V11">
@@ -1436,13 +1437,13 @@
         <v/>
       </c>
       <c r="Z11" t="str">
-        <v/>
+        <v>场所</v>
       </c>
       <c r="AA11" t="str">
-        <v/>
+        <v>- 20251001121212 - 收货地址：养生SPA (养生spa) (场所) - 商品: 一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×11;一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×1;三得利 沁桃水饮料 550ml/瓶×5;三得利 沁葡水白葡萄味饮料550ml/瓶果味饮品休闲饮料×5;</v>
       </c>
       <c r="AB11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="AC11" t="str">
         <v>中</v>
@@ -1451,108 +1452,12 @@
         <v/>
       </c>
       <c r="AE11" t="str">
-        <v>2025-11-07</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
-        <v>小钱</v>
-      </c>
-      <c r="B12" t="str">
-        <v>居民身份证</v>
-      </c>
-      <c r="C12" t="str">
-        <v>310227199002301010</v>
-      </c>
-      <c r="D12" t="str">
-        <v>15286493075</v>
-      </c>
-      <c r="E12" t="str">
-        <v>新桥镇新中街10000号100010室</v>
-      </c>
-      <c r="F12" t="str">
-        <v>新桥镇新中街10000号100010室</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="str">
-        <v>中</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v>同住人</v>
-      </c>
-      <c r="L12" t="str" xml:space="preserve">
-        <v xml:space="preserve"> 新桥镇新中街10000号100010室 - 跟1人同住: 
-姓名： 赵十, 证件号：310227199510011230, 手机号：15123456789， 社保：上海咨询有限公司, 前科： 殴打他人</v>
-      </c>
-      <c r="M12" t="str">
-        <v>新桥派出所</v>
-      </c>
-      <c r="N12" t="str">
-        <v>卖淫,嫖娼,介绍卖淫</v>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v>- 20251001121212 - 商品: &lt;span style='color:darkorange'&gt;一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×11;一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×1;三得利 沁桃水饮料 550ml/瓶×5;三得利 沁葡水白葡萄味饮料550ml/瓶果味饮品休闲饮料×5;&lt;/span&gt; - 收货地址：养生SPA (养生spa)</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>上海实业有限公司</v>
-      </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <v>1</v>
-      </c>
-      <c r="T12" t="str">
-        <v>1</v>
-      </c>
-      <c r="U12" t="str">
-        <v>1</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12" t="str">
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <v/>
-      </c>
-      <c r="Z12" t="str">
-        <v>场所</v>
-      </c>
-      <c r="AA12" t="str">
-        <v>- 20251001121212 - 收货地址：养生SPA (养生spa) (场所) - 商品: 一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×11;一次性浴巾加大加50*100cm厚独立包装旅行出差毛巾宾馆酒店美容院压缩浴巾 /条×1;三得利 沁桃水饮料 550ml/瓶×5;三得利 沁葡水白葡萄味饮料550ml/瓶果味饮品休闲饮料×5;</v>
-      </c>
-      <c r="AB12" t="str">
-        <v>是</v>
-      </c>
-      <c r="AC12" t="str">
-        <v>中</v>
-      </c>
-      <c r="AD12" t="str">
-        <v/>
-      </c>
-      <c r="AE12" t="str">
         <v>2025-11-07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/yellow-server/data/results/result.xlsx
+++ b/yellow-server/data/results/result.xlsx
@@ -561,16 +561,16 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="str">
-        <v/>
+        <v>- 2025-05-14 18:15:33-2025-05-15 13:10:14: 张三 和 孙一(男）证件号：310227199810011020在松江商务宾馆101房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y2" t="str">
-        <v/>
+        <v>- 2025-05-14 18:15:33-2025-05-15 13:10:14 张三 入住 松江商务宾馆101房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z2" t="str">
         <v>小区</v>
@@ -588,7 +588,7 @@
         <v/>
       </c>
       <c r="AE2" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -611,7 +611,7 @@
         <v>新桥镇新中街10000号10002室</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
         <v>高</v>
@@ -657,16 +657,16 @@
         <v>1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="str">
-        <v/>
+        <v>- 2025-03-26 13:16:38-2025-03-26 15:46:44: 老王 和 孙二(男）证件号：310227199810011021在松江商务宾馆102房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y3" t="str">
-        <v/>
+        <v>- 2025-03-26 13:16:38-2025-03-26 15:46:44 老王 入住 松江商务宾馆102房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z3" t="str">
         <v>场所</v>
@@ -680,11 +680,12 @@
       <c r="AC3" t="str">
         <v>高</v>
       </c>
-      <c r="AD3" t="str">
-        <v/>
+      <c r="AD3" t="str" xml:space="preserve">
+        <v xml:space="preserve">账户 310227199002301002 收：1000元
+- 20250529154757 收到来自 085e9858e15934197a59978e6@wx.tenpay.com 的转账</v>
       </c>
       <c r="AE3" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -753,16 +754,16 @@
         <v>1</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="str">
-        <v/>
+        <v>- 2025-04-01 11:42:49-2025-04-01 15:44:58: 老张 和 孙三(男）证件号：310227199810011022在松江商务宾馆103房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y4" t="str">
-        <v/>
+        <v>- 2025-04-01 11:42:49-2025-04-01 15:44:58 老张 入住 松江商务宾馆103房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z4" t="str">
         <v>小区</v>
@@ -780,7 +781,7 @@
         <v/>
       </c>
       <c r="AE4" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -849,16 +850,16 @@
         <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="str">
-        <v/>
+        <v>- 2025-05-15 21:29:24-2025-05-17 11:21:31: 老李 和 孙四(男）证件号：310227199810011023在松江商务宾馆104房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y5" t="str">
-        <v/>
+        <v>- 2025-05-15 21:29:24-2025-05-17 11:21:31 老李 入住 松江商务宾馆104房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z5" t="str">
         <v>小区</v>
@@ -876,7 +877,7 @@
         <v/>
       </c>
       <c r="AE5" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -945,16 +946,16 @@
         <v>1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="str">
-        <v/>
+        <v>- 2025-04-19 05:53:33- : 小王 和 孙五(男）证件号：310227199810011024在松江商务宾馆105房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y6" t="str">
-        <v/>
+        <v>- 2025-04-19 05:53:33-  小王 入住 松江商务宾馆105房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z6" t="str">
         <v>小区</v>
@@ -972,7 +973,7 @@
         <v/>
       </c>
       <c r="AE6" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -995,10 +996,10 @@
         <v>新桥镇新中街10000号10006室</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="str">
-        <v>低</v>
+        <v>中</v>
       </c>
       <c r="I7" t="str">
         <v>桃园路90号</v>
@@ -1023,7 +1024,7 @@
         <v>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现松江区桃园路90号小李等人有卖淫嫖娼的行为。</v>
       </c>
       <c r="P7" t="str">
-        <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (127)</v>
+        <v>- 20251001121212 - 商品: &lt;span style='color:darkorange'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (127)</v>
       </c>
       <c r="Q7" t="str">
         <v>上海电子商务有限公司</v>
@@ -1041,16 +1042,16 @@
         <v>1</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="str">
-        <v/>
+        <v>- 2025-06-15 04:49:04-2025-06-15 16:58:54: 小李 和 孙六(男）证件号：310227199810011025在松江商务宾馆106房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y7" t="str">
-        <v/>
+        <v>- 2025-06-15 04:49:04-2025-06-15 16:58:54 小李 入住 松江商务宾馆106房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z7" t="str">
         <v>小区</v>
@@ -1062,13 +1063,14 @@
         <v>是</v>
       </c>
       <c r="AC7" t="str">
-        <v>中</v>
-      </c>
-      <c r="AD7" t="str">
-        <v/>
+        <v>高</v>
+      </c>
+      <c r="AD7" t="str" xml:space="preserve">
+        <v xml:space="preserve">账户 310227199002301006 收：12000元
+- 20250525124330 收到来自 085e9858ec5a0277bffa6ff7b@wx.tenpay.com 的转账</v>
       </c>
       <c r="AE7" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -1094,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="str">
-        <v>低</v>
+        <v>中</v>
       </c>
       <c r="I8" t="str">
         <v>桃园路90号</v>
@@ -1119,7 +1121,7 @@
         <v>2025年5月14日，我所民警接线索举报称上海市松江区桃园路90号有卖淫嫖娼的情况，遂至上址检查，并经出示证件将相关人员传唤至所作进一步调查。</v>
       </c>
       <c r="P8" t="str">
-        <v>- 20251001121212 - 商品: &lt;span style='color:darkgreen'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (128)</v>
+        <v>- 20251001121212 - 商品: &lt;span style='color:darkorange'&gt;[福人]金刚藤胶囊0.5g*42粒/盒×1;[可孚]阴道冲洗器(中号伸缩式KF-S01)150ml/袋×2;[何医生]妇洁舒冲洗器50ml/盒×1;&lt;/span&gt; - 收货地址：松江公寓 (128)</v>
       </c>
       <c r="Q8" t="str">
         <v>上海电子商务有限公司</v>
@@ -1137,16 +1139,16 @@
         <v>1</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="str">
-        <v/>
+        <v>- 2025-05-27 22:28:33-2025-05-29 14:38:50: 小胡 和 孙七(男）证件号：310227199810011026在松江商务宾馆107房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y8" t="str">
-        <v/>
+        <v>- 2025-05-27 22:28:33-2025-05-29 14:38:50 小胡 入住 松江商务宾馆107房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z8" t="str">
         <v>小区</v>
@@ -1164,7 +1166,7 @@
         <v/>
       </c>
       <c r="AE8" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -1187,7 +1189,7 @@
         <v>新桥镇新中街10000号10008室</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="str">
         <v>中</v>
@@ -1233,16 +1235,16 @@
         <v>1</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="str">
-        <v/>
+        <v>- 2025-04-14 22:22:42- : 小刚 和 孙八(男）证件号：310227199810011027在松江商务宾馆108房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y9" t="str">
-        <v/>
+        <v>- 2025-04-14 22:22:42-  小刚 入住 松江商务宾馆108房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z9" t="str">
         <v>小区</v>
@@ -1254,13 +1256,14 @@
         <v>是</v>
       </c>
       <c r="AC9" t="str">
-        <v>中</v>
-      </c>
-      <c r="AD9" t="str">
-        <v/>
+        <v>高</v>
+      </c>
+      <c r="AD9" t="str" xml:space="preserve">
+        <v xml:space="preserve">账户 310227199002301008 收：600元
+- 20250519181113 收到来自 085e9858e358b923d3b881e99@wx.tenpay.com 的转账</v>
       </c>
       <c r="AE9" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -1283,7 +1286,7 @@
         <v>新桥镇新中街10000号10009室</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="str">
         <v>中</v>
@@ -1329,16 +1332,16 @@
         <v>1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18: 小金 和 孙九(男）证件号：310227199810011028在松江商务宾馆109房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y10" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18 小金 入住 松江商务宾馆109房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z10" t="str">
         <v>小区</v>
@@ -1350,13 +1353,15 @@
         <v>是</v>
       </c>
       <c r="AC10" t="str">
-        <v>中</v>
-      </c>
-      <c r="AD10" t="str">
-        <v/>
+        <v>高</v>
+      </c>
+      <c r="AD10" t="str" xml:space="preserve">
+        <v xml:space="preserve">账户 310227199002301009 收：600元
+- 20250531224132 收到来自 085e9858ee8c9b52eee923931@wx.tenpay.com 的转账
+- 20250531222637 收到来自 085e9858e5e108034435d1930@wx.tenpay.com 的转账</v>
       </c>
       <c r="AE10" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -1425,16 +1430,16 @@
         <v>1</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18: 小钱 和 孙十(男）证件号：310227199810011029在松江商务宾馆110房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Y11" t="str">
-        <v/>
+        <v>- 2025-05-20 21:34:39-2025-05-21 22:53:18 小钱 入住 松江商务宾馆110房间-地址：松江区新桥镇新桥路1000号</v>
       </c>
       <c r="Z11" t="str">
         <v>场所</v>
@@ -1452,7 +1457,7 @@
         <v/>
       </c>
       <c r="AE11" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-10</v>
       </c>
     </row>
   </sheetData>
